--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -390,10 +390,10 @@
     <t xml:space="preserve"> Valor Unidade</t>
   </si>
   <si>
-    <t>Sup. Banana</t>
-  </si>
-  <si>
-    <t>NÃO</t>
+    <t>Chaveiro Kamila</t>
+  </si>
+  <si>
+    <t>SIM</t>
   </si>
 </sst>
 </file>
@@ -1715,19 +1715,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>35.144869333333332</v>
+        <v>13.67056</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>35.144869333333332</v>
+        <v>13.67056</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>26.358651999999999</v>
+        <v>10.25292</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>26.358651999999999</v>
+        <v>10.25292</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1745,19 +1745,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>30.751760666666666</v>
+        <v>11.961740000000001</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>153.75880333333333</v>
+        <v>59.808700000000002</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>21.965543333333333</v>
+        <v>8.5441000000000003</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>109.82771666666666</v>
+        <v>42.720500000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1765,7 +1765,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>66.16</v>
+        <v>18</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1775,19 +1775,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>26.358651999999999</v>
+        <v>10.25292</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>263.58652000000001</v>
+        <v>102.5292</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>17.572434666666666</v>
+        <v>6.8352799999999991</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>175.72434666666666</v>
+        <v>68.352799999999988</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1795,7 +1795,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1805,19 +1805,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>21.965543333333333</v>
+        <v>8.5441000000000003</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>549.13858333333337</v>
+        <v>213.60250000000002</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>13.179326</v>
+        <v>5.1264599999999998</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>329.48314999999997</v>
+        <v>128.16149999999999</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1835,19 +1835,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>19.329678133333335</v>
+        <v>7.5188080000000008</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>966.48390666666671</v>
+        <v>375.94040000000007</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>10.543460800000002</v>
+        <v>4.1011680000000013</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>527.17304000000013</v>
+        <v>205.05840000000006</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1865,19 +1865,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>17.572434666666666</v>
+        <v>6.83528</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>1757.2434666666666</v>
+        <v>683.52800000000002</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>8.7862173333333331</v>
+        <v>3.41764</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>878.62173333333328</v>
+        <v>341.76400000000001</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1895,19 +1895,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>15.815191199999999</v>
+        <v>6.1517520000000001</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>7907.5955999999996</v>
+        <v>3075.8760000000002</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>7.0289738666666661</v>
+        <v>2.7341120000000001</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>3514.4869333333331</v>
+        <v>1367.056</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1919,19 +1919,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>14.936569466666667</v>
+        <v>5.8099879999999997</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>14936.569466666666</v>
+        <v>5809.9879999999994</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>6.1503521333333335</v>
+        <v>2.3923479999999997</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>6150.3521333333338</v>
+        <v>2392.3479999999995</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1949,19 +1949,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>14.057947733333334</v>
+        <v>5.4682240000000002</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>35144.869333333336</v>
+        <v>13670.560000000001</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>5.2717304000000009</v>
+        <v>2.0505840000000002</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>13179.326000000003</v>
+        <v>5126.46</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>6.2785840000000004</v>
+        <v>1.7081999999999999</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.66</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>1.8476333333333335</v>
+        <v>0.83983333333333332</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>8.7862173333333331</v>
+        <v>2.8480333333333334</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>8.7862173333333331</v>
+        <v>3.41764</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>8.7862173333333331</v>
+        <v>3.41764</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>1.7572434666666665</v>
+        <v>0.68352800000000002</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2092,7 @@
     <row r="9" spans="2:4" ht="15.75" thickBot="1">
       <c r="B9" s="41" t="str">
         <f>Calculadora!B4</f>
-        <v>Sup. Banana</v>
+        <v>Chaveiro Kamila</v>
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="43"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>35.144869333333332</v>
+        <v>13.67056</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>30.751760666666666</v>
+        <v>11.961740000000001</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2153,11 +2153,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>26.358651999999999</v>
+        <v>10.25292</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2167,11 +2167,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>21.965543333333333</v>
+        <v>8.5441000000000003</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2181,11 +2181,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>19.329678133333335</v>
+        <v>7.5188080000000008</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2195,11 +2195,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>17.572434666666666</v>
+        <v>6.83528</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2209,11 +2209,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>15.815191199999999</v>
+        <v>6.1517520000000001</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>14.936569466666667</v>
+        <v>5.8099879999999997</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>93</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2237,11 +2237,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>14.057947733333334</v>
+        <v>5.4682240000000002</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>230</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">Calculadora!$G$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Impressão!$A$1:$E$29</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -390,10 +390,10 @@
     <t xml:space="preserve"> Valor Unidade</t>
   </si>
   <si>
-    <t>Chaveiro Kamila</t>
-  </si>
-  <si>
-    <t>SIM</t>
+    <t>Coelho Pascoa GR</t>
+  </si>
+  <si>
+    <t>NÃO</t>
   </si>
 </sst>
 </file>
@@ -417,11 +417,13 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1715,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>13.67056</v>
+        <v>99.122349333333332</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>13.67056</v>
+        <v>99.122349333333332</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>10.25292</v>
+        <v>74.341762000000003</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>10.25292</v>
+        <v>74.341762000000003</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1745,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>11.961740000000001</v>
+        <v>86.732055666666668</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>59.808700000000002</v>
+        <v>433.66027833333334</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>8.5441000000000003</v>
+        <v>61.951468333333338</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>42.720500000000001</v>
+        <v>309.75734166666666</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1765,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>18</v>
+        <v>191.46</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1775,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>10.25292</v>
+        <v>74.341762000000003</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>102.5292</v>
+        <v>743.41762000000006</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>6.8352799999999991</v>
+        <v>49.561174666666673</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>68.352799999999988</v>
+        <v>495.6117466666667</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1795,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1805,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>8.5441000000000003</v>
+        <v>61.951468333333331</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>213.60250000000002</v>
+        <v>1548.7867083333333</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>5.1264599999999998</v>
+        <v>37.170880999999994</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>128.16149999999999</v>
+        <v>929.27202499999987</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1835,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>7.5188080000000008</v>
+        <v>54.517292133333335</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>375.94040000000007</v>
+        <v>2725.8646066666665</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>4.1011680000000013</v>
+        <v>29.736704800000002</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>205.05840000000006</v>
+        <v>1486.8352400000001</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1865,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>6.83528</v>
+        <v>49.561174666666666</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>683.52800000000002</v>
+        <v>4956.1174666666666</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>3.41764</v>
+        <v>24.780587333333333</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>341.76400000000001</v>
+        <v>2478.0587333333333</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1895,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>6.1517520000000001</v>
+        <v>44.605057199999997</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>3075.8760000000002</v>
+        <v>22302.528599999998</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>2.7341120000000001</v>
+        <v>19.824469866666664</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>1367.056</v>
+        <v>9912.2349333333314</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1919,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>5.8099879999999997</v>
+        <v>42.126998466666663</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>5809.9879999999994</v>
+        <v>42126.998466666664</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>2.3923479999999997</v>
+        <v>17.34641113333333</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>2392.3479999999995</v>
+        <v>17346.411133333331</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1949,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>5.4682240000000002</v>
+        <v>39.648939733333336</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>13670.560000000001</v>
+        <v>99122.349333333346</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>2.0505840000000002</v>
+        <v>14.868352400000003</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>5126.46</v>
+        <v>37170.881000000008</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1970,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>1.7081999999999999</v>
+        <v>18.169554000000002</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1985,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.3</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1994,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>0.83983333333333332</v>
+        <v>4.8710333333333331</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2005,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>2.8480333333333334</v>
+        <v>24.780587333333333</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2014,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>3.41764</v>
+        <v>24.780587333333333</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2023,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>3.41764</v>
+        <v>24.780587333333333</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2038,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>0.68352800000000002</v>
+        <v>4.9561174666666661</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2094,7 @@
     <row r="9" spans="2:4" ht="15.75" thickBot="1">
       <c r="B9" s="41" t="str">
         <f>Calculadora!B4</f>
-        <v>Chaveiro Kamila</v>
+        <v>Coelho Pascoa GR</v>
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="43"/>
@@ -2125,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>13.67056</v>
+        <v>99.122349333333332</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2139,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>11.961740000000001</v>
+        <v>86.732055666666668</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2153,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>10.25292</v>
+        <v>74.341762000000003</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2167,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>8.5441000000000003</v>
+        <v>61.951468333333331</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2181,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>7.5188080000000008</v>
+        <v>54.517292133333335</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2195,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>6.83528</v>
+        <v>49.561174666666666</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2209,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>6.1517520000000001</v>
+        <v>44.605057199999997</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>22</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2223,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>5.8099879999999997</v>
+        <v>42.126998466666663</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>43</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2237,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>5.4682240000000002</v>
+        <v>39.648939733333336</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>105</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -390,10 +390,10 @@
     <t xml:space="preserve"> Valor Unidade</t>
   </si>
   <si>
-    <t>Coelho Pascoa GR</t>
-  </si>
-  <si>
     <t>NÃO</t>
+  </si>
+  <si>
+    <t>Coelho Pascoa Medio</t>
   </si>
 </sst>
 </file>
@@ -1654,7 +1654,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="85.5703125" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" customWidth="1"/>
@@ -1707,7 +1707,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>99.122349333333332</v>
+        <v>75.758045333333342</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>99.122349333333332</v>
+        <v>75.758045333333342</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>74.341762000000003</v>
+        <v>56.818534000000007</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>74.341762000000003</v>
+        <v>56.818534000000007</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>86.732055666666668</v>
+        <v>66.288289666666671</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>433.66027833333334</v>
+        <v>331.44144833333337</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>61.951468333333338</v>
+        <v>47.348778333333335</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>309.75734166666666</v>
+        <v>236.74389166666668</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>191.46</v>
+        <v>140.72</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>74.341762000000003</v>
+        <v>56.818534000000007</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>743.41762000000006</v>
+        <v>568.18534000000011</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>49.561174666666673</v>
+        <v>37.879022666666671</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>495.6117466666667</v>
+        <v>378.79022666666674</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>5.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>61.951468333333331</v>
+        <v>47.348778333333343</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>1548.7867083333333</v>
+        <v>1183.7194583333335</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>37.170880999999994</v>
+        <v>28.409267000000007</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>929.27202499999987</v>
+        <v>710.23167500000022</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>54.517292133333335</v>
+        <v>41.666924933333341</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>2725.8646066666665</v>
+        <v>2083.346246666667</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>29.736704800000002</v>
+        <v>22.727413600000006</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>1486.8352400000001</v>
+        <v>1136.3706800000002</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1857,7 +1857,7 @@
         <v>110</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>49.561174666666666</v>
+        <v>37.879022666666671</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>4956.1174666666666</v>
+        <v>3787.9022666666669</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>24.780587333333333</v>
+        <v>18.939511333333336</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>2478.0587333333333</v>
+        <v>1893.9511333333335</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>44.605057199999997</v>
+        <v>34.091120400000008</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>22302.528599999998</v>
+        <v>17045.560200000004</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>19.824469866666664</v>
+        <v>15.151609066666673</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>9912.2349333333314</v>
+        <v>7575.8045333333366</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>42.126998466666663</v>
+        <v>32.19716926666667</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>42126.998466666664</v>
+        <v>32197.169266666671</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>17.34641113333333</v>
+        <v>13.257657933333334</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>17346.411133333331</v>
+        <v>13257.657933333334</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>39.648939733333336</v>
+        <v>30.303218133333338</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>99122.349333333346</v>
+        <v>75758.045333333343</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>14.868352400000003</v>
+        <v>11.363706800000003</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>37170.881000000008</v>
+        <v>28409.267000000007</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>18.169554000000002</v>
+        <v>13.354328000000002</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>4.8710333333333331</v>
+        <v>4.1151833333333334</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>24.780587333333333</v>
+        <v>18.939511333333336</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>24.780587333333333</v>
+        <v>18.939511333333336</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>24.780587333333333</v>
+        <v>18.939511333333336</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>4.9561174666666661</v>
+        <v>3.7879022666666673</v>
       </c>
     </row>
   </sheetData>
@@ -2094,7 +2094,7 @@
     <row r="9" spans="2:4" ht="15.75" thickBot="1">
       <c r="B9" s="41" t="str">
         <f>Calculadora!B4</f>
-        <v>Coelho Pascoa GR</v>
+        <v>Coelho Pascoa Medio</v>
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="43"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>99.122349333333332</v>
+        <v>75.758045333333342</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>86.732055666666668</v>
+        <v>66.288289666666671</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>74.341762000000003</v>
+        <v>56.818534000000007</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>61.951468333333331</v>
+        <v>47.348778333333343</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>54.517292133333335</v>
+        <v>41.666924933333341</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>49.561174666666666</v>
+        <v>37.879022666666671</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>44.605057199999997</v>
+        <v>34.091120400000008</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>42.126998466666663</v>
+        <v>32.19716926666667</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>243</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>39.648939733333336</v>
+        <v>30.303218133333338</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>605</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>75.758045333333342</v>
+        <v>29.777999999999999</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>75.758045333333342</v>
+        <v>29.777999999999999</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>56.818534000000007</v>
+        <v>22.333500000000001</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>56.818534000000007</v>
+        <v>22.333500000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>66.288289666666671</v>
+        <v>26.05575</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>331.44144833333337</v>
+        <v>130.27875</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>47.348778333333335</v>
+        <v>18.611249999999998</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>236.74389166666668</v>
+        <v>93.056249999999991</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>140.72</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>56.818534000000007</v>
+        <v>22.333500000000001</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>568.18534000000011</v>
+        <v>223.33500000000001</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>37.879022666666671</v>
+        <v>14.889000000000001</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>378.79022666666674</v>
+        <v>148.89000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>4.9000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>47.348778333333343</v>
+        <v>18.611249999999998</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>1183.7194583333335</v>
+        <v>465.28124999999994</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>28.409267000000007</v>
+        <v>11.166749999999999</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>710.23167500000022</v>
+        <v>279.16874999999999</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>41.666924933333341</v>
+        <v>16.3779</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>2083.346246666667</v>
+        <v>818.89499999999998</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>22.727413600000006</v>
+        <v>8.9334000000000007</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>1136.3706800000002</v>
+        <v>446.67</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>37.879022666666671</v>
+        <v>14.888999999999999</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>3787.9022666666669</v>
+        <v>1488.8999999999999</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>18.939511333333336</v>
+        <v>7.4444999999999997</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>1893.9511333333335</v>
+        <v>744.44999999999993</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>34.091120400000008</v>
+        <v>13.4001</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>17045.560200000004</v>
+        <v>6700.05</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>15.151609066666673</v>
+        <v>5.9556000000000004</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>7575.8045333333366</v>
+        <v>2977.8</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>32.19716926666667</v>
+        <v>12.65565</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>32197.169266666671</v>
+        <v>12655.65</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>13.257657933333334</v>
+        <v>5.2111499999999999</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>13257.657933333334</v>
+        <v>5211.1499999999996</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>30.303218133333338</v>
+        <v>11.911200000000001</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>75758.045333333343</v>
+        <v>29778.000000000004</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>11.363706800000003</v>
+        <v>4.4667000000000012</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>28409.267000000007</v>
+        <v>11166.750000000004</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>13.354328000000002</v>
+        <v>2.6572</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>4.1151833333333334</v>
+        <v>3.5272999999999999</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>18.939511333333336</v>
+        <v>7.4444999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>18.939511333333336</v>
+        <v>7.4444999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>18.939511333333336</v>
+        <v>7.4444999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>3.7879022666666673</v>
+        <v>1.4888999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>75.758045333333342</v>
+        <v>29.777999999999999</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>66.288289666666671</v>
+        <v>26.05575</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>56.818534000000007</v>
+        <v>22.333500000000001</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>47.348778333333343</v>
+        <v>18.611249999999998</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>41.666924933333341</v>
+        <v>16.3779</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>37.879022666666671</v>
+        <v>14.888999999999999</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>34.091120400000008</v>
+        <v>13.4001</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>32.19716926666667</v>
+        <v>12.65565</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>205</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>30.303218133333338</v>
+        <v>11.911200000000001</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>511</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -390,10 +390,10 @@
     <t xml:space="preserve"> Valor Unidade</t>
   </si>
   <si>
-    <t>NÃO</t>
-  </si>
-  <si>
-    <t>Coelho Pascoa Medio</t>
+    <t>GHOST</t>
+  </si>
+  <si>
+    <t>SIM</t>
   </si>
 </sst>
 </file>
@@ -1707,7 +1707,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>29.777999999999999</v>
+        <v>11.093358400000001</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>29.777999999999999</v>
+        <v>11.093358400000001</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>22.333500000000001</v>
+        <v>8.3200188000000015</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>22.333500000000001</v>
+        <v>8.3200188000000015</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>26.05575</v>
+        <v>9.7066886000000014</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>130.27875</v>
+        <v>48.533443000000005</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>18.611249999999998</v>
+        <v>6.9333490000000015</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>93.056249999999991</v>
+        <v>34.666745000000006</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>28</v>
+        <v>9.82</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>22.333500000000001</v>
+        <v>8.3200188000000015</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>223.33500000000001</v>
+        <v>83.200188000000011</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>14.889000000000001</v>
+        <v>5.5466792000000016</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>148.89000000000001</v>
+        <v>55.466792000000012</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>4.2</v>
+        <v>1.21</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>18.611249999999998</v>
+        <v>6.9333490000000007</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>465.28124999999994</v>
+        <v>173.33372500000002</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>11.166749999999999</v>
+        <v>4.1600093999999999</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>279.16874999999999</v>
+        <v>104.000235</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>16.3779</v>
+        <v>6.1013471200000016</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>818.89499999999998</v>
+        <v>305.06735600000007</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>8.9334000000000007</v>
+        <v>3.3280075200000012</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>446.67</v>
+        <v>166.40037600000005</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1857,7 +1857,7 @@
         <v>110</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>14.888999999999999</v>
+        <v>5.5466792000000007</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>1488.8999999999999</v>
+        <v>554.66792000000009</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>7.4444999999999997</v>
+        <v>2.7733396000000003</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>744.44999999999993</v>
+        <v>277.33396000000005</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>13.4001</v>
+        <v>4.9920112800000007</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>6700.05</v>
+        <v>2496.0056400000003</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>5.9556000000000004</v>
+        <v>2.2186716800000004</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>2977.8</v>
+        <v>1109.3358400000002</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>12.65565</v>
+        <v>4.7146773200000007</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>12655.65</v>
+        <v>4714.6773200000007</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>5.2111499999999999</v>
+        <v>1.9413377200000004</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>5211.1499999999996</v>
+        <v>1941.3377200000004</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>11.911200000000001</v>
+        <v>4.4373433600000007</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>29778.000000000004</v>
+        <v>11093.358400000001</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>4.4667000000000012</v>
+        <v>1.6640037600000004</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>11166.750000000004</v>
+        <v>4160.0094000000008</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>2.6572</v>
+        <v>0.93191800000000014</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>1.26</v>
+        <v>0.36299999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>3.5272999999999999</v>
+        <v>1.0161983333333333</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>7.4444999999999997</v>
+        <v>2.3111163333333336</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>7.4444999999999997</v>
+        <v>2.7733396000000003</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>7.4444999999999997</v>
+        <v>2.7733396000000003</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>1.4888999999999999</v>
+        <v>0.55466792000000009</v>
       </c>
     </row>
   </sheetData>
@@ -2094,7 +2094,7 @@
     <row r="9" spans="2:4" ht="15.75" thickBot="1">
       <c r="B9" s="41" t="str">
         <f>Calculadora!B4</f>
-        <v>Coelho Pascoa Medio</v>
+        <v>GHOST</v>
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="43"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>29.777999999999999</v>
+        <v>11.093358400000001</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>26.05575</v>
+        <v>9.7066886000000014</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>22.333500000000001</v>
+        <v>8.3200188000000015</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>18.611249999999998</v>
+        <v>6.9333490000000007</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>16.3779</v>
+        <v>6.1013471200000016</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>14.888999999999999</v>
+        <v>5.5466792000000007</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>13.4001</v>
+        <v>4.9920112800000007</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>88</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>12.65565</v>
+        <v>4.7146773200000007</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>176</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>11.911200000000001</v>
+        <v>4.4373433600000007</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>438</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">Calculadora!$G$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Impressão!$A$1:$E$29</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -390,10 +390,10 @@
     <t xml:space="preserve"> Valor Unidade</t>
   </si>
   <si>
-    <t>GHOST</t>
-  </si>
-  <si>
-    <t>SIM</t>
+    <t>Nome Personalizado</t>
+  </si>
+  <si>
+    <t>NÃO</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1471,7 @@
         <v>57</v>
       </c>
       <c r="B7" s="22">
-        <v>94.9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>11.093358400000001</v>
+        <v>89.724666666666664</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>11.093358400000001</v>
+        <v>89.724666666666664</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>8.3200188000000015</v>
+        <v>67.293499999999995</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>8.3200188000000015</v>
+        <v>67.293499999999995</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>9.7066886000000014</v>
+        <v>78.509083333333336</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>48.533443000000005</v>
+        <v>392.54541666666671</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>6.9333490000000015</v>
+        <v>56.077916666666667</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>34.666745000000006</v>
+        <v>280.38958333333335</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>9.82</v>
+        <v>188</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>8.3200188000000015</v>
+        <v>67.293499999999995</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>83.200188000000011</v>
+        <v>672.93499999999995</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>5.5466792000000016</v>
+        <v>44.862333333333325</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>55.466792000000012</v>
+        <v>448.62333333333322</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>1.21</v>
+        <v>5</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>6.9333490000000007</v>
+        <v>56.077916666666667</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>173.33372500000002</v>
+        <v>1401.9479166666667</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>4.1600093999999999</v>
+        <v>33.646749999999997</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>104.000235</v>
+        <v>841.16874999999993</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>6.1013471200000016</v>
+        <v>49.34856666666667</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>305.06735600000007</v>
+        <v>2467.4283333333333</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>3.3280075200000012</v>
+        <v>26.917400000000004</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>166.40037600000005</v>
+        <v>1345.8700000000001</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>5.5466792000000007</v>
+        <v>44.862333333333332</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>554.66792000000009</v>
+        <v>4486.2333333333336</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>2.7733396000000003</v>
+        <v>22.431166666666666</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>277.33396000000005</v>
+        <v>2243.1166666666668</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>4.9920112800000007</v>
+        <v>40.376100000000001</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>2496.0056400000003</v>
+        <v>20188.05</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>2.2186716800000004</v>
+        <v>17.944933333333335</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>1109.3358400000002</v>
+        <v>8972.4666666666672</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>4.7146773200000007</v>
+        <v>38.132983333333328</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>4714.6773200000007</v>
+        <v>38132.98333333333</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>1.9413377200000004</v>
+        <v>15.701816666666662</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>1941.3377200000004</v>
+        <v>15701.816666666662</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>4.4373433600000007</v>
+        <v>35.88986666666667</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>11093.358400000001</v>
+        <v>89724.666666666672</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>1.6640037600000004</v>
+        <v>13.458700000000004</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>4160.0094000000008</v>
+        <v>33646.750000000007</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>0.93191800000000014</v>
+        <v>16.731999999999999</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.36299999999999999</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>1.0161983333333333</v>
+        <v>4.1991666666666667</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>2.3111163333333336</v>
+        <v>22.431166666666666</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>2.7733396000000003</v>
+        <v>22.431166666666666</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>2.7733396000000003</v>
+        <v>22.431166666666666</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>0.55466792000000009</v>
+        <v>4.4862333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -2094,7 +2094,7 @@
     <row r="9" spans="2:4" ht="15.75" thickBot="1">
       <c r="B9" s="41" t="str">
         <f>Calculadora!B4</f>
-        <v>GHOST</v>
+        <v>Nome Personalizado</v>
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="43"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>11.093358400000001</v>
+        <v>89.724666666666664</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>9.7066886000000014</v>
+        <v>78.509083333333336</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>8.3200188000000015</v>
+        <v>67.293499999999995</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>6.9333490000000007</v>
+        <v>56.077916666666667</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>6.1013471200000016</v>
+        <v>49.34856666666667</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>5.5466792000000007</v>
+        <v>44.862333333333332</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>4.9920112800000007</v>
+        <v>40.376100000000001</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>26</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>4.7146773200000007</v>
+        <v>38.132983333333328</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>51</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>4.4373433600000007</v>
+        <v>35.88986666666667</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>127</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>89.724666666666664</v>
+        <v>38.242000000000004</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>89.724666666666664</v>
+        <v>38.242000000000004</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>67.293499999999995</v>
+        <v>28.681500000000003</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>67.293499999999995</v>
+        <v>28.681500000000003</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>78.509083333333336</v>
+        <v>33.461750000000002</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>392.54541666666671</v>
+        <v>167.30875</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>56.077916666666667</v>
+        <v>23.901250000000001</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>280.38958333333335</v>
+        <v>119.50625000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>67.293499999999995</v>
+        <v>28.681500000000003</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>672.93499999999995</v>
+        <v>286.81500000000005</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>44.862333333333325</v>
+        <v>19.121000000000002</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>448.62333333333322</v>
+        <v>191.21000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>56.077916666666667</v>
+        <v>23.901250000000005</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>1401.9479166666667</v>
+        <v>597.53125000000011</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>33.646749999999997</v>
+        <v>14.340750000000003</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>841.16874999999993</v>
+        <v>358.51875000000007</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>49.34856666666667</v>
+        <v>21.033100000000005</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>2467.4283333333333</v>
+        <v>1051.6550000000002</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>26.917400000000004</v>
+        <v>11.472600000000003</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>1345.8700000000001</v>
+        <v>573.63000000000022</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>44.862333333333332</v>
+        <v>19.121000000000002</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>4486.2333333333336</v>
+        <v>1912.1000000000001</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>22.431166666666666</v>
+        <v>9.5605000000000011</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>2243.1166666666668</v>
+        <v>956.05000000000007</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>40.376100000000001</v>
+        <v>17.208900000000003</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>20188.05</v>
+        <v>8604.4500000000025</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>17.944933333333335</v>
+        <v>7.6484000000000023</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>8972.4666666666672</v>
+        <v>3824.2000000000012</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>38.132983333333328</v>
+        <v>16.252850000000002</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>38132.98333333333</v>
+        <v>16252.850000000002</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>15.701816666666662</v>
+        <v>6.6923500000000011</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>15701.816666666662</v>
+        <v>6692.3500000000013</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>35.88986666666667</v>
+        <v>15.296800000000003</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>89724.666666666672</v>
+        <v>38242.000000000007</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>13.458700000000004</v>
+        <v>5.7363000000000017</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>33646.750000000007</v>
+        <v>14340.750000000004</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>16.731999999999999</v>
+        <v>6.1410000000000009</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>1.5</v>
+        <v>0.89999999999999991</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>4.1991666666666667</v>
+        <v>2.5194999999999999</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>22.431166666666666</v>
+        <v>9.5605000000000011</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>22.431166666666666</v>
+        <v>9.5605000000000011</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>22.431166666666666</v>
+        <v>9.5605000000000011</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>4.4862333333333337</v>
+        <v>1.9121000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>89.724666666666664</v>
+        <v>38.242000000000004</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>78.509083333333336</v>
+        <v>33.461750000000002</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>67.293499999999995</v>
+        <v>28.681500000000003</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>56.077916666666667</v>
+        <v>23.901250000000005</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>49.34856666666667</v>
+        <v>21.033100000000005</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>44.862333333333332</v>
+        <v>19.121000000000002</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>40.376100000000001</v>
+        <v>17.208900000000003</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>105</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>38.132983333333328</v>
+        <v>16.252850000000002</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>209</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>35.88986666666667</v>
+        <v>15.296800000000003</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>522</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>38.242000000000004</v>
+        <v>10.255333333333333</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>38.242000000000004</v>
+        <v>10.255333333333333</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>28.681500000000003</v>
+        <v>7.6914999999999996</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>28.681500000000003</v>
+        <v>7.6914999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>33.461750000000002</v>
+        <v>8.9734166666666653</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>167.30875</v>
+        <v>44.867083333333326</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>23.901250000000001</v>
+        <v>6.4095833333333321</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>119.50625000000001</v>
+        <v>32.047916666666659</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>28.681500000000003</v>
+        <v>7.6914999999999996</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>286.81500000000005</v>
+        <v>76.914999999999992</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>19.121000000000002</v>
+        <v>5.1276666666666664</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>191.21000000000004</v>
+        <v>51.276666666666664</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>23.901250000000005</v>
+        <v>6.409583333333333</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>597.53125000000011</v>
+        <v>160.23958333333331</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>14.340750000000003</v>
+        <v>3.8457499999999998</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>358.51875000000007</v>
+        <v>96.143749999999997</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>21.033100000000005</v>
+        <v>5.6404333333333332</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>1051.6550000000002</v>
+        <v>282.02166666666665</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>11.472600000000003</v>
+        <v>3.0766</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>573.63000000000022</v>
+        <v>153.83000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>19.121000000000002</v>
+        <v>5.1276666666666664</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>1912.1000000000001</v>
+        <v>512.76666666666665</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>9.5605000000000011</v>
+        <v>2.5638333333333332</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>956.05000000000007</v>
+        <v>256.38333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>17.208900000000003</v>
+        <v>4.6148999999999996</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>8604.4500000000025</v>
+        <v>2307.4499999999998</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>7.6484000000000023</v>
+        <v>2.0510666666666664</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>3824.2000000000012</v>
+        <v>1025.5333333333331</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>16.252850000000002</v>
+        <v>4.3585166666666666</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>16252.850000000002</v>
+        <v>4358.5166666666664</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>6.6923500000000011</v>
+        <v>1.7946833333333334</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>6692.3500000000013</v>
+        <v>1794.6833333333334</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>15.296800000000003</v>
+        <v>4.1021333333333336</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>38242.000000000007</v>
+        <v>10255.333333333334</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>5.7363000000000017</v>
+        <v>1.5383000000000004</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>14340.750000000004</v>
+        <v>3845.7500000000009</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>6.1410000000000009</v>
+        <v>1.4239999999999999</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.89999999999999991</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>2.5194999999999999</v>
+        <v>0.83983333333333332</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>9.5605000000000011</v>
+        <v>2.5638333333333332</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>9.5605000000000011</v>
+        <v>2.5638333333333332</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>9.5605000000000011</v>
+        <v>2.5638333333333332</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>1.9121000000000004</v>
+        <v>0.51276666666666659</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>38.242000000000004</v>
+        <v>10.255333333333333</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>33.461750000000002</v>
+        <v>8.9734166666666653</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>28.681500000000003</v>
+        <v>7.6914999999999996</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>23.901250000000005</v>
+        <v>6.409583333333333</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>21.033100000000005</v>
+        <v>5.6404333333333332</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>19.121000000000002</v>
+        <v>5.1276666666666664</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>17.208900000000003</v>
+        <v>4.6148999999999996</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>63</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>16.252850000000002</v>
+        <v>4.3585166666666666</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>126</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>15.296800000000003</v>
+        <v>4.1021333333333336</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>313</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">Calculadora!$G$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Impressão!$A$1:$E$29</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>10.255333333333333</v>
+        <v>78.757333333333335</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>10.255333333333333</v>
+        <v>78.757333333333335</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>7.6914999999999996</v>
+        <v>59.067999999999998</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>7.6914999999999996</v>
+        <v>59.067999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>8.9734166666666653</v>
+        <v>68.912666666666667</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>44.867083333333326</v>
+        <v>344.56333333333333</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>6.4095833333333321</v>
+        <v>49.223333333333329</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>32.047916666666659</v>
+        <v>246.11666666666665</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>7.6914999999999996</v>
+        <v>59.067999999999998</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>76.914999999999992</v>
+        <v>590.67999999999995</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>5.1276666666666664</v>
+        <v>39.37866666666666</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>51.276666666666664</v>
+        <v>393.78666666666663</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>6.409583333333333</v>
+        <v>49.223333333333336</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>160.23958333333331</v>
+        <v>1230.5833333333335</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>3.8457499999999998</v>
+        <v>29.534000000000002</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>96.143749999999997</v>
+        <v>738.35</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>5.6404333333333332</v>
+        <v>43.316533333333339</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>282.02166666666665</v>
+        <v>2165.8266666666668</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>3.0766</v>
+        <v>23.627200000000006</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>153.83000000000001</v>
+        <v>1181.3600000000004</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>5.1276666666666664</v>
+        <v>39.378666666666668</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>512.76666666666665</v>
+        <v>3937.8666666666668</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>2.5638333333333332</v>
+        <v>19.689333333333334</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>256.38333333333333</v>
+        <v>1968.9333333333334</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>4.6148999999999996</v>
+        <v>35.440800000000003</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>2307.4499999999998</v>
+        <v>17720.400000000001</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>2.0510666666666664</v>
+        <v>15.751466666666669</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>1025.5333333333331</v>
+        <v>7875.7333333333345</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>4.3585166666666666</v>
+        <v>33.471866666666664</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>4358.5166666666664</v>
+        <v>33471.866666666661</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>1.7946833333333334</v>
+        <v>13.78253333333333</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>1794.6833333333334</v>
+        <v>13782.533333333329</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>4.1021333333333336</v>
+        <v>31.502933333333335</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>10255.333333333334</v>
+        <v>78757.333333333343</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>1.5383000000000004</v>
+        <v>11.813600000000001</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>3845.7500000000009</v>
+        <v>29534.000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>1.4239999999999999</v>
+        <v>15.13</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>0.83983333333333332</v>
+        <v>3.3593333333333333</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>2.5638333333333332</v>
+        <v>19.689333333333334</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>2.5638333333333332</v>
+        <v>19.689333333333334</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>2.5638333333333332</v>
+        <v>19.689333333333334</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>0.51276666666666659</v>
+        <v>3.9378666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>10.255333333333333</v>
+        <v>78.757333333333335</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>8.9734166666666653</v>
+        <v>68.912666666666667</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>7.6914999999999996</v>
+        <v>59.067999999999998</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>6.409583333333333</v>
+        <v>49.223333333333336</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>5.6404333333333332</v>
+        <v>43.316533333333339</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>5.1276666666666664</v>
+        <v>39.378666666666668</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>4.6148999999999996</v>
+        <v>35.440800000000003</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>22</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>4.3585166666666666</v>
+        <v>33.471866666666664</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>43</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>4.1021333333333336</v>
+        <v>31.502933333333335</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>105</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">Calculadora!$G$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Impressão!$A$1:$E$29</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -393,7 +393,7 @@
     <t>Nome Personalizado</t>
   </si>
   <si>
-    <t>NÃO</t>
+    <t>SIM</t>
   </si>
 </sst>
 </file>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>78.757333333333335</v>
+        <v>10.95736</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>78.757333333333335</v>
+        <v>10.95736</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>59.067999999999998</v>
+        <v>8.2180199999999992</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>59.067999999999998</v>
+        <v>8.2180199999999992</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>68.912666666666667</v>
+        <v>9.5876900000000003</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>344.56333333333333</v>
+        <v>47.938450000000003</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>49.223333333333329</v>
+        <v>6.8483499999999999</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>246.11666666666665</v>
+        <v>34.241749999999996</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>59.067999999999998</v>
+        <v>8.2180199999999992</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>590.67999999999995</v>
+        <v>82.180199999999985</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>39.37866666666666</v>
+        <v>5.4786799999999989</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>393.78666666666663</v>
+        <v>54.786799999999985</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>49.223333333333336</v>
+        <v>6.8483499999999999</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>1230.5833333333335</v>
+        <v>171.20875000000001</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>29.534000000000002</v>
+        <v>4.1090099999999996</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>738.35</v>
+        <v>102.72524999999999</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>43.316533333333339</v>
+        <v>6.026548</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>2165.8266666666668</v>
+        <v>301.32740000000001</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>23.627200000000006</v>
+        <v>3.2872080000000001</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>1181.3600000000004</v>
+        <v>164.3604</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>39.378666666666668</v>
+        <v>5.4786799999999998</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>3937.8666666666668</v>
+        <v>547.86799999999994</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>19.689333333333334</v>
+        <v>2.7393399999999999</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>1968.9333333333334</v>
+        <v>273.93399999999997</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>35.440800000000003</v>
+        <v>4.9308119999999995</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>17720.400000000001</v>
+        <v>2465.4059999999999</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>15.751466666666669</v>
+        <v>2.1914719999999996</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>7875.7333333333345</v>
+        <v>1095.7359999999999</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>33.471866666666664</v>
+        <v>4.6568779999999999</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>33471.866666666661</v>
+        <v>4656.8779999999997</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>13.78253333333333</v>
+        <v>1.917538</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>13782.533333333329</v>
+        <v>1917.538</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>31.502933333333335</v>
+        <v>4.3829440000000002</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>78757.333333333343</v>
+        <v>10957.36</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>11.813600000000001</v>
+        <v>1.6436040000000003</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>29534.000000000004</v>
+        <v>4109.0100000000011</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>15.13</v>
+        <v>0.80099999999999993</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>1.2</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>3.3593333333333333</v>
+        <v>1.0917833333333333</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>19.689333333333334</v>
+        <v>2.2827833333333332</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>19.689333333333334</v>
+        <v>2.7393399999999999</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>19.689333333333334</v>
+        <v>2.7393399999999999</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>3.9378666666666668</v>
+        <v>0.54786800000000002</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>78.757333333333335</v>
+        <v>10.95736</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>68.912666666666667</v>
+        <v>9.5876900000000003</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>59.067999999999998</v>
+        <v>8.2180199999999992</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>49.223333333333336</v>
+        <v>6.8483499999999999</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>43.316533333333339</v>
+        <v>6.026548</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>39.378666666666668</v>
+        <v>5.4786799999999998</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>35.440800000000003</v>
+        <v>4.9308119999999995</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>84</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>33.471866666666664</v>
+        <v>4.6568779999999999</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>168</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>31.502933333333335</v>
+        <v>4.3829440000000002</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>418</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">Calculadora!$G$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Impressão!$A$1:$E$29</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -393,7 +393,7 @@
     <t>Nome Personalizado</t>
   </si>
   <si>
-    <t>SIM</t>
+    <t>NÃO</t>
   </si>
 </sst>
 </file>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>10.95736</v>
+        <v>7.7490933333333327</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>10.95736</v>
+        <v>7.7490933333333327</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>8.2180199999999992</v>
+        <v>5.8118199999999991</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>8.2180199999999992</v>
+        <v>5.8118199999999991</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>9.5876900000000003</v>
+        <v>6.7804566666666659</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>47.938450000000003</v>
+        <v>33.90228333333333</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>6.8483499999999999</v>
+        <v>4.8431833333333323</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>34.241749999999996</v>
+        <v>24.215916666666661</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>9</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>8.2180199999999992</v>
+        <v>5.8118199999999991</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>82.180199999999985</v>
+        <v>58.118199999999987</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>5.4786799999999989</v>
+        <v>3.8745466666666659</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>54.786799999999985</v>
+        <v>38.745466666666658</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>6.8483499999999999</v>
+        <v>4.8431833333333332</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>171.20875000000001</v>
+        <v>121.07958333333333</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>4.1090099999999996</v>
+        <v>2.90591</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>102.72524999999999</v>
+        <v>72.647750000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>6.026548</v>
+        <v>4.2620013333333331</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>301.32740000000001</v>
+        <v>213.10006666666666</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>3.2872080000000001</v>
+        <v>2.3247279999999999</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>164.3604</v>
+        <v>116.23639999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>5.4786799999999998</v>
+        <v>3.8745466666666664</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>547.86799999999994</v>
+        <v>387.45466666666664</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>2.7393399999999999</v>
+        <v>1.9372733333333332</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>273.93399999999997</v>
+        <v>193.72733333333332</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>4.9308119999999995</v>
+        <v>3.4870919999999996</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>2465.4059999999999</v>
+        <v>1743.5459999999998</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>2.1914719999999996</v>
+        <v>1.5498186666666665</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>1095.7359999999999</v>
+        <v>774.90933333333328</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>4.6568779999999999</v>
+        <v>3.2933646666666663</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>4656.8779999999997</v>
+        <v>3293.3646666666664</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>1.917538</v>
+        <v>1.3560913333333331</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>1917.538</v>
+        <v>1356.0913333333331</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>4.3829440000000002</v>
+        <v>3.0996373333333334</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>10957.36</v>
+        <v>7749.0933333333332</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>1.6436040000000003</v>
+        <v>1.1623640000000002</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>4109.0100000000011</v>
+        <v>2905.9100000000003</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>0.80099999999999993</v>
+        <v>0.79744000000000004</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>1.0917833333333333</v>
+        <v>0.83983333333333332</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>2.2827833333333332</v>
+        <v>1.9372733333333332</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>2.7393399999999999</v>
+        <v>1.9372733333333332</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>2.7393399999999999</v>
+        <v>1.9372733333333332</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>0.54786800000000002</v>
+        <v>0.38745466666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>10.95736</v>
+        <v>7.7490933333333327</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>9.5876900000000003</v>
+        <v>6.7804566666666659</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>8.2180199999999992</v>
+        <v>5.8118199999999991</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>6.8483499999999999</v>
+        <v>4.8431833333333332</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>6.026548</v>
+        <v>4.2620013333333331</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>5.4786799999999998</v>
+        <v>3.8745466666666664</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>4.9308119999999995</v>
+        <v>3.4870919999999996</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>4.6568779999999999</v>
+        <v>3.2933646666666663</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>4.3829440000000002</v>
+        <v>3.0996373333333334</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>136</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>7.7490933333333327</v>
+        <v>8.8313333333333333</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>7.7490933333333327</v>
+        <v>8.8313333333333333</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>5.8118199999999991</v>
+        <v>6.6234999999999999</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>5.8118199999999991</v>
+        <v>6.6234999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>6.7804566666666659</v>
+        <v>7.7274166666666666</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>33.90228333333333</v>
+        <v>38.637083333333337</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>4.8431833333333323</v>
+        <v>5.5195833333333333</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>24.215916666666661</v>
+        <v>27.597916666666666</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>8.9600000000000009</v>
+        <v>12</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>5.8118199999999991</v>
+        <v>6.6234999999999999</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>58.118199999999987</v>
+        <v>66.234999999999999</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>3.8745466666666659</v>
+        <v>4.4156666666666666</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>38.745466666666658</v>
+        <v>44.156666666666666</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>4.8431833333333332</v>
+        <v>5.5195833333333333</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>121.07958333333333</v>
+        <v>137.98958333333334</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>2.90591</v>
+        <v>3.31175</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>72.647750000000002</v>
+        <v>82.793750000000003</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>4.2620013333333331</v>
+        <v>4.8572333333333333</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>213.10006666666666</v>
+        <v>242.86166666666668</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>2.3247279999999999</v>
+        <v>2.6494</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>116.23639999999999</v>
+        <v>132.47</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>3.8745466666666664</v>
+        <v>4.4156666666666666</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>387.45466666666664</v>
+        <v>441.56666666666666</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>1.9372733333333332</v>
+        <v>2.2078333333333333</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>193.72733333333332</v>
+        <v>220.78333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>3.4870919999999996</v>
+        <v>3.9741</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>1743.5459999999998</v>
+        <v>1987.05</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>1.5498186666666665</v>
+        <v>1.7662666666666667</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>774.90933333333328</v>
+        <v>883.13333333333333</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>3.2933646666666663</v>
+        <v>3.7533166666666666</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>3293.3646666666664</v>
+        <v>3753.3166666666666</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>1.3560913333333331</v>
+        <v>1.5454833333333333</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>1356.0913333333331</v>
+        <v>1545.4833333333333</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>3.0996373333333334</v>
+        <v>3.5325333333333333</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>7749.0933333333332</v>
+        <v>8831.3333333333339</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>1.1623640000000002</v>
+        <v>1.3247</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>2905.9100000000003</v>
+        <v>3311.75</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>0.79744000000000004</v>
+        <v>1.0680000000000001</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>1.9372733333333332</v>
+        <v>2.2078333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>1.9372733333333332</v>
+        <v>2.2078333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>1.9372733333333332</v>
+        <v>2.2078333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>0.38745466666666667</v>
+        <v>0.44156666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>7.7490933333333327</v>
+        <v>8.8313333333333333</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>6.7804566666666659</v>
+        <v>7.7274166666666666</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>5.8118199999999991</v>
+        <v>6.6234999999999999</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>4.8431833333333332</v>
+        <v>5.5195833333333333</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>4.2620013333333331</v>
+        <v>4.8572333333333333</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>3.8745466666666664</v>
+        <v>4.4156666666666666</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>3.4870919999999996</v>
+        <v>3.9741</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>3.2933646666666663</v>
+        <v>3.7533166666666666</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>3.0996373333333334</v>
+        <v>3.5325333333333333</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">Calculadora!$G$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Impressão!$A$1:$E$29</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>8.8313333333333333</v>
+        <v>8.063133333333333</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>8.8313333333333333</v>
+        <v>8.063133333333333</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>6.6234999999999999</v>
+        <v>6.0473499999999998</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>6.6234999999999999</v>
+        <v>6.0473499999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>7.7274166666666666</v>
+        <v>7.0552416666666664</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>38.637083333333337</v>
+        <v>35.276208333333329</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>5.5195833333333333</v>
+        <v>5.0394583333333332</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>27.597916666666666</v>
+        <v>25.197291666666665</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>6.6234999999999999</v>
+        <v>6.0473499999999998</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>66.234999999999999</v>
+        <v>60.473500000000001</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>4.4156666666666666</v>
+        <v>4.0315666666666665</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>44.156666666666666</v>
+        <v>40.315666666666665</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>5.5195833333333333</v>
+        <v>5.0394583333333332</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>137.98958333333334</v>
+        <v>125.98645833333333</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>3.31175</v>
+        <v>3.0236749999999999</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>82.793750000000003</v>
+        <v>75.591875000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>4.8572333333333333</v>
+        <v>4.4347233333333334</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>242.86166666666668</v>
+        <v>221.73616666666666</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>2.6494</v>
+        <v>2.4189400000000001</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>132.47</v>
+        <v>120.947</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>4.4156666666666666</v>
+        <v>4.0315666666666665</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>441.56666666666666</v>
+        <v>403.15666666666664</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>2.2078333333333333</v>
+        <v>2.0157833333333333</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>220.78333333333333</v>
+        <v>201.57833333333332</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>3.9741</v>
+        <v>3.6284100000000001</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>1987.05</v>
+        <v>1814.2050000000002</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>1.7662666666666667</v>
+        <v>1.6126266666666669</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>883.13333333333333</v>
+        <v>806.31333333333339</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>3.7533166666666666</v>
+        <v>3.4268316666666663</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>3753.3166666666666</v>
+        <v>3426.8316666666665</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>1.5454833333333333</v>
+        <v>1.411048333333333</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>1545.4833333333333</v>
+        <v>1411.0483333333329</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>3.5325333333333333</v>
+        <v>3.2252533333333333</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>8831.3333333333339</v>
+        <v>8063.1333333333332</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>1.3247</v>
+        <v>1.20947</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>3311.75</v>
+        <v>3023.6750000000002</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>1.0680000000000001</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>0.83983333333333332</v>
+        <v>1.0917833333333333</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>2.2078333333333333</v>
+        <v>2.0157833333333333</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>2.2078333333333333</v>
+        <v>2.0157833333333333</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>2.2078333333333333</v>
+        <v>2.0157833333333333</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>0.44156666666666666</v>
+        <v>0.40315666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>8.8313333333333333</v>
+        <v>8.063133333333333</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>7.7274166666666666</v>
+        <v>7.0552416666666664</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>6.6234999999999999</v>
+        <v>6.0473499999999998</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>5.5195833333333333</v>
+        <v>5.0394583333333332</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>4.8572333333333333</v>
+        <v>4.4347233333333334</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>4.4156666666666666</v>
+        <v>4.0315666666666665</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>3.9741</v>
+        <v>3.6284100000000001</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>3.7533166666666666</v>
+        <v>3.4268316666666663</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>3.5325333333333333</v>
+        <v>3.2252533333333333</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>105</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>8.063133333333333</v>
+        <v>72.948933333333329</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>8.063133333333333</v>
+        <v>72.948933333333329</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>6.0473499999999998</v>
+        <v>54.711699999999993</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>6.0473499999999998</v>
+        <v>54.711699999999993</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>7.0552416666666664</v>
+        <v>63.830316666666661</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>35.276208333333329</v>
+        <v>319.15158333333329</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>5.0394583333333332</v>
+        <v>45.593083333333325</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>25.197291666666665</v>
+        <v>227.96541666666661</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>6.0473499999999998</v>
+        <v>54.711699999999993</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>60.473500000000001</v>
+        <v>547.11699999999996</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>4.0315666666666665</v>
+        <v>36.474466666666657</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>40.315666666666665</v>
+        <v>364.7446666666666</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>1.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>5.0394583333333332</v>
+        <v>45.593083333333333</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>125.98645833333333</v>
+        <v>1139.8270833333333</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>3.0236749999999999</v>
+        <v>27.35585</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>75.591875000000002</v>
+        <v>683.89625000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>4.4347233333333334</v>
+        <v>40.121913333333332</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>221.73616666666666</v>
+        <v>2006.0956666666666</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>2.4189400000000001</v>
+        <v>21.884679999999999</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>120.947</v>
+        <v>1094.2339999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>4.0315666666666665</v>
+        <v>36.474466666666665</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>403.15666666666664</v>
+        <v>3647.4466666666663</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>2.0157833333333333</v>
+        <v>18.237233333333332</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>201.57833333333332</v>
+        <v>1823.7233333333331</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>3.6284100000000001</v>
+        <v>32.827019999999997</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>1814.2050000000002</v>
+        <v>16413.509999999998</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>1.6126266666666669</v>
+        <v>14.589786666666665</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>806.31333333333339</v>
+        <v>7294.8933333333325</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>3.4268316666666663</v>
+        <v>31.003296666666664</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>3426.8316666666665</v>
+        <v>31003.296666666665</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>1.411048333333333</v>
+        <v>12.766063333333332</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>1411.0483333333329</v>
+        <v>12766.063333333332</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>3.2252533333333333</v>
+        <v>29.179573333333334</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>8063.1333333333332</v>
+        <v>72948.933333333334</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>1.20947</v>
+        <v>10.942340000000002</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>3023.6750000000002</v>
+        <v>27355.850000000002</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>0.53400000000000003</v>
+        <v>12.994</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.39</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>1.0917833333333333</v>
+        <v>3.8632333333333331</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>2.0157833333333333</v>
+        <v>18.237233333333332</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>2.0157833333333333</v>
+        <v>18.237233333333332</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>2.0157833333333333</v>
+        <v>18.237233333333332</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>0.40315666666666666</v>
+        <v>3.6474466666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>8.063133333333333</v>
+        <v>72.948933333333329</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>7.0552416666666664</v>
+        <v>63.830316666666661</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>6.0473499999999998</v>
+        <v>54.711699999999993</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>5.0394583333333332</v>
+        <v>45.593083333333333</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>4.4347233333333334</v>
+        <v>40.121913333333332</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>4.0315666666666665</v>
+        <v>36.474466666666665</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>3.6284100000000001</v>
+        <v>32.827019999999997</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>28</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>3.4268316666666663</v>
+        <v>31.003296666666664</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>55</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>3.2252533333333333</v>
+        <v>29.179573333333334</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>136</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>72.948933333333329</v>
+        <v>13.3032</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>72.948933333333329</v>
+        <v>13.3032</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>54.711699999999993</v>
+        <v>9.9773999999999994</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>54.711699999999993</v>
+        <v>9.9773999999999994</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>63.830316666666661</v>
+        <v>11.6403</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>319.15158333333329</v>
+        <v>58.201499999999996</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>45.593083333333325</v>
+        <v>8.3144999999999989</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>227.96541666666661</v>
+        <v>41.572499999999991</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>54.711699999999993</v>
+        <v>9.9773999999999994</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>547.11699999999996</v>
+        <v>99.774000000000001</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>36.474466666666657</v>
+        <v>6.6515999999999993</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>364.7446666666666</v>
+        <v>66.515999999999991</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>4.5999999999999996</v>
+        <v>1.2</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>45.593083333333333</v>
+        <v>8.3145000000000007</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>1139.8270833333333</v>
+        <v>207.86250000000001</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>27.35585</v>
+        <v>4.9887000000000006</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>683.89625000000001</v>
+        <v>124.71750000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>40.121913333333332</v>
+        <v>7.3167600000000004</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>2006.0956666666666</v>
+        <v>365.83800000000002</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>21.884679999999999</v>
+        <v>3.9909600000000003</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>1094.2339999999999</v>
+        <v>199.548</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>36.474466666666665</v>
+        <v>6.6516000000000002</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>3647.4466666666663</v>
+        <v>665.16</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>18.237233333333332</v>
+        <v>3.3258000000000001</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>1823.7233333333331</v>
+        <v>332.58</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>32.827019999999997</v>
+        <v>5.98644</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>16413.509999999998</v>
+        <v>2993.22</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>14.589786666666665</v>
+        <v>2.6606399999999999</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>7294.8933333333325</v>
+        <v>1330.32</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>31.003296666666664</v>
+        <v>5.6538599999999999</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>31003.296666666665</v>
+        <v>5653.86</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>12.766063333333332</v>
+        <v>2.3280599999999998</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>12766.063333333332</v>
+        <v>2328.06</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>29.179573333333334</v>
+        <v>5.3212800000000007</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>72948.933333333334</v>
+        <v>13303.200000000003</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>10.942340000000002</v>
+        <v>1.9954800000000006</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>27355.850000000002</v>
+        <v>4988.7000000000016</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>12.994</v>
+        <v>1.958</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>1.38</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>3.8632333333333331</v>
+        <v>1.0078</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>18.237233333333332</v>
+        <v>3.3258000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>18.237233333333332</v>
+        <v>3.3258000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>18.237233333333332</v>
+        <v>3.3258000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>3.6474466666666667</v>
+        <v>0.66516000000000008</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>72.948933333333329</v>
+        <v>13.3032</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>63.830316666666661</v>
+        <v>11.6403</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>54.711699999999993</v>
+        <v>9.9773999999999994</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>45.593083333333333</v>
+        <v>8.3145000000000007</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>40.121913333333332</v>
+        <v>7.3167600000000004</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>36.474466666666665</v>
+        <v>6.6516000000000002</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>32.827019999999997</v>
+        <v>5.98644</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>97</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>31.003296666666664</v>
+        <v>5.6538599999999999</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>193</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>29.179573333333334</v>
+        <v>5.3212800000000007</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>480</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" firstSheet="2" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>13.3032</v>
+        <v>72.948933333333329</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>13.3032</v>
+        <v>72.948933333333329</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>9.9773999999999994</v>
+        <v>54.711699999999993</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>9.9773999999999994</v>
+        <v>54.711699999999993</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>11.6403</v>
+        <v>63.830316666666661</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>58.201499999999996</v>
+        <v>319.15158333333329</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>8.3144999999999989</v>
+        <v>45.593083333333325</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>41.572499999999991</v>
+        <v>227.96541666666661</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>9.9773999999999994</v>
+        <v>54.711699999999993</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>99.774000000000001</v>
+        <v>547.11699999999996</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>6.6515999999999993</v>
+        <v>36.474466666666657</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>66.515999999999991</v>
+        <v>364.7446666666666</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>1.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>8.3145000000000007</v>
+        <v>45.593083333333333</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>207.86250000000001</v>
+        <v>1139.8270833333333</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>4.9887000000000006</v>
+        <v>27.35585</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>124.71750000000002</v>
+        <v>683.89625000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>7.3167600000000004</v>
+        <v>40.121913333333332</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>365.83800000000002</v>
+        <v>2006.0956666666666</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>3.9909600000000003</v>
+        <v>21.884679999999999</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>199.548</v>
+        <v>1094.2339999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>6.6516000000000002</v>
+        <v>36.474466666666665</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>665.16</v>
+        <v>3647.4466666666663</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>3.3258000000000001</v>
+        <v>18.237233333333332</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>332.58</v>
+        <v>1823.7233333333331</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>5.98644</v>
+        <v>32.827019999999997</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>2993.22</v>
+        <v>16413.509999999998</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>2.6606399999999999</v>
+        <v>14.589786666666665</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>1330.32</v>
+        <v>7294.8933333333325</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>5.6538599999999999</v>
+        <v>31.003296666666664</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>5653.86</v>
+        <v>31003.296666666665</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>2.3280599999999998</v>
+        <v>12.766063333333332</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>2328.06</v>
+        <v>12766.063333333332</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>5.3212800000000007</v>
+        <v>29.179573333333334</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>13303.200000000003</v>
+        <v>72948.933333333334</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>1.9954800000000006</v>
+        <v>10.942340000000002</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>4988.7000000000016</v>
+        <v>27355.850000000002</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>1.958</v>
+        <v>12.994</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>1.0078</v>
+        <v>3.8632333333333331</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>3.3258000000000001</v>
+        <v>18.237233333333332</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>3.3258000000000001</v>
+        <v>18.237233333333332</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>3.3258000000000001</v>
+        <v>18.237233333333332</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>0.66516000000000008</v>
+        <v>3.6474466666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>13.3032</v>
+        <v>72.948933333333329</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>11.6403</v>
+        <v>63.830316666666661</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>9.9773999999999994</v>
+        <v>54.711699999999993</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>8.3145000000000007</v>
+        <v>45.593083333333333</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>7.3167600000000004</v>
+        <v>40.121913333333332</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>6.6516000000000002</v>
+        <v>36.474466666666665</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>5.98644</v>
+        <v>32.827019999999997</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>26</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>5.6538599999999999</v>
+        <v>31.003296666666664</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>51</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>5.3212800000000007</v>
+        <v>29.179573333333334</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>126</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>72.948933333333329</v>
+        <v>109.16733333333333</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>72.948933333333329</v>
+        <v>109.16733333333333</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>54.711699999999993</v>
+        <v>81.875500000000002</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>54.711699999999993</v>
+        <v>81.875500000000002</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>63.830316666666661</v>
+        <v>95.521416666666667</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>319.15158333333329</v>
+        <v>477.60708333333332</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>45.593083333333325</v>
+        <v>68.229583333333338</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>227.96541666666661</v>
+        <v>341.14791666666667</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>54.711699999999993</v>
+        <v>81.875500000000002</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>547.11699999999996</v>
+        <v>818.755</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>36.474466666666657</v>
+        <v>54.583666666666673</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>364.7446666666666</v>
+        <v>545.8366666666667</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>4.5999999999999996</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>45.593083333333333</v>
+        <v>68.229583333333338</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>1139.8270833333333</v>
+        <v>1705.7395833333335</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>27.35585</v>
+        <v>40.937750000000008</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>683.89625000000001</v>
+        <v>1023.4437500000003</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>40.121913333333332</v>
+        <v>60.042033333333336</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>2006.0956666666666</v>
+        <v>3002.1016666666669</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>21.884679999999999</v>
+        <v>32.750200000000007</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>1094.2339999999999</v>
+        <v>1637.5100000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>36.474466666666665</v>
+        <v>54.583666666666666</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>3647.4466666666663</v>
+        <v>5458.3666666666668</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>18.237233333333332</v>
+        <v>27.291833333333333</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>1823.7233333333331</v>
+        <v>2729.1833333333334</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>32.827019999999997</v>
+        <v>49.125300000000003</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>16413.509999999998</v>
+        <v>24562.65</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>14.589786666666665</v>
+        <v>21.83346666666667</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>7294.8933333333325</v>
+        <v>10916.733333333335</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>31.003296666666664</v>
+        <v>46.396116666666664</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>31003.296666666665</v>
+        <v>46396.116666666661</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>12.766063333333332</v>
+        <v>19.104283333333331</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>12766.063333333332</v>
+        <v>19104.283333333333</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>29.179573333333334</v>
+        <v>43.666933333333333</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>72948.933333333334</v>
+        <v>109167.33333333333</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>10.942340000000002</v>
+        <v>16.3751</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>27355.850000000002</v>
+        <v>40937.75</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>12.994</v>
+        <v>19.312999999999999</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>3.8632333333333331</v>
+        <v>5.8788333333333336</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>18.237233333333332</v>
+        <v>27.291833333333333</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>18.237233333333332</v>
+        <v>27.291833333333333</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>18.237233333333332</v>
+        <v>27.291833333333333</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>3.6474466666666667</v>
+        <v>5.4583666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>72.948933333333329</v>
+        <v>109.16733333333333</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>63.830316666666661</v>
+        <v>95.521416666666667</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>54.711699999999993</v>
+        <v>81.875500000000002</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>45.593083333333333</v>
+        <v>68.229583333333338</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>40.121913333333332</v>
+        <v>60.042033333333336</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>36.474466666666665</v>
+        <v>54.583666666666666</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>32.827019999999997</v>
+        <v>49.125300000000003</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>97</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>31.003296666666664</v>
+        <v>46.396116666666664</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>193</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>29.179573333333334</v>
+        <v>43.666933333333333</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>480</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">Calculadora!$G$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Impressão!$A$1:$E$29</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1471,7 +1471,7 @@
         <v>57</v>
       </c>
       <c r="B7" s="22">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>109.16733333333333</v>
+        <v>110.03533333333334</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>109.16733333333333</v>
+        <v>110.03533333333334</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>81.875500000000002</v>
+        <v>82.526499999999999</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>81.875500000000002</v>
+        <v>82.526499999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>95.521416666666667</v>
+        <v>96.28091666666667</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>477.60708333333332</v>
+        <v>481.40458333333333</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>68.229583333333338</v>
+        <v>68.772083333333342</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>341.14791666666667</v>
+        <v>343.86041666666671</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>81.875500000000002</v>
+        <v>82.526499999999999</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>818.755</v>
+        <v>825.26499999999999</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>54.583666666666673</v>
+        <v>55.017666666666663</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>545.8366666666667</v>
+        <v>550.17666666666662</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>68.229583333333338</v>
+        <v>68.772083333333342</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>1705.7395833333335</v>
+        <v>1719.3020833333335</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>40.937750000000008</v>
+        <v>41.263250000000006</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>1023.4437500000003</v>
+        <v>1031.5812500000002</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>60.042033333333336</v>
+        <v>60.519433333333339</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>3002.1016666666669</v>
+        <v>3025.9716666666668</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>32.750200000000007</v>
+        <v>33.010600000000004</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>1637.5100000000002</v>
+        <v>1650.5300000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>54.583666666666666</v>
+        <v>55.01766666666667</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>5458.3666666666668</v>
+        <v>5501.7666666666673</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>27.291833333333333</v>
+        <v>27.508833333333335</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>2729.1833333333334</v>
+        <v>2750.8833333333337</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>49.125300000000003</v>
+        <v>49.515900000000002</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>24562.65</v>
+        <v>24757.95</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>21.83346666666667</v>
+        <v>22.007066666666667</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>10916.733333333335</v>
+        <v>11003.533333333333</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>46.396116666666664</v>
+        <v>46.765016666666668</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>46396.116666666661</v>
+        <v>46765.01666666667</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>19.104283333333331</v>
+        <v>19.256183333333333</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>19104.283333333333</v>
+        <v>19256.183333333334</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>43.666933333333333</v>
+        <v>44.014133333333341</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>109167.33333333333</v>
+        <v>110035.33333333336</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>16.3751</v>
+        <v>16.505300000000005</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>40937.75</v>
+        <v>41263.250000000015</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>19.312999999999999</v>
+        <v>19.53</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>27.291833333333333</v>
+        <v>27.508833333333335</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>27.291833333333333</v>
+        <v>27.508833333333335</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>27.291833333333333</v>
+        <v>27.508833333333335</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>5.4583666666666666</v>
+        <v>5.5017666666666676</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>109.16733333333333</v>
+        <v>110.03533333333334</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>95.521416666666667</v>
+        <v>96.28091666666667</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>81.875500000000002</v>
+        <v>82.526499999999999</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>68.229583333333338</v>
+        <v>68.772083333333342</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>60.042033333333336</v>
+        <v>60.519433333333339</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>54.583666666666666</v>
+        <v>55.01766666666667</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>49.125300000000003</v>
+        <v>49.515900000000002</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>46.396116666666664</v>
+        <v>46.765016666666668</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>43.666933333333333</v>
+        <v>44.014133333333341</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4455" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">Calculadora!$G$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Impressão!$A$1:$E$29</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>110.03533333333334</v>
+        <v>11.158999999999999</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>110.03533333333334</v>
+        <v>11.158999999999999</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>82.526499999999999</v>
+        <v>8.3692499999999992</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>82.526499999999999</v>
+        <v>8.3692499999999992</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>96.28091666666667</v>
+        <v>9.7641249999999999</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>481.40458333333333</v>
+        <v>48.820625</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>68.772083333333342</v>
+        <v>6.9743750000000002</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>343.86041666666671</v>
+        <v>34.871875000000003</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>217</v>
+        <v>12</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>82.526499999999999</v>
+        <v>8.3692499999999992</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>825.26499999999999</v>
+        <v>83.692499999999995</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>55.017666666666663</v>
+        <v>5.5794999999999995</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>550.17666666666662</v>
+        <v>55.794999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>68.772083333333342</v>
+        <v>6.9743749999999993</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>1719.3020833333335</v>
+        <v>174.35937499999997</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>41.263250000000006</v>
+        <v>4.1846249999999996</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>1031.5812500000002</v>
+        <v>104.61562499999999</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>60.519433333333339</v>
+        <v>6.1374500000000003</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>3025.9716666666668</v>
+        <v>306.8725</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>33.010600000000004</v>
+        <v>3.3477000000000006</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>1650.5300000000002</v>
+        <v>167.38500000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>55.01766666666667</v>
+        <v>5.5794999999999995</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>5501.7666666666673</v>
+        <v>557.94999999999993</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>27.508833333333335</v>
+        <v>2.7897499999999997</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>2750.8833333333337</v>
+        <v>278.97499999999997</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>49.515900000000002</v>
+        <v>5.0215499999999995</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>24757.95</v>
+        <v>2510.7749999999996</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>22.007066666666667</v>
+        <v>2.2317999999999998</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>11003.533333333333</v>
+        <v>1115.8999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>46.765016666666668</v>
+        <v>4.7425749999999995</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>46765.01666666667</v>
+        <v>4742.5749999999998</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>19.256183333333333</v>
+        <v>1.9528249999999998</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>19256.183333333334</v>
+        <v>1952.8249999999998</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>44.014133333333341</v>
+        <v>4.4635999999999996</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>110035.33333333336</v>
+        <v>11158.999999999998</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>16.505300000000005</v>
+        <v>1.6738499999999998</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>41263.250000000015</v>
+        <v>4184.625</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>19.53</v>
+        <v>1.08</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>2.1</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>5.8788333333333336</v>
+        <v>1.2597499999999999</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>27.508833333333335</v>
+        <v>2.7897499999999997</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>27.508833333333335</v>
+        <v>2.7897499999999997</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>27.508833333333335</v>
+        <v>2.7897499999999997</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>5.5017666666666676</v>
+        <v>0.55794999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>110.03533333333334</v>
+        <v>11.158999999999999</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>96.28091666666667</v>
+        <v>9.7641249999999999</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:4">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>82.526499999999999</v>
+        <v>8.3692499999999992</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>68.772083333333342</v>
+        <v>6.9743749999999993</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>60.519433333333339</v>
+        <v>6.1374500000000003</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>55.01766666666667</v>
+        <v>5.5794999999999995</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>49.515900000000002</v>
+        <v>5.0215499999999995</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>147</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>46.765016666666668</v>
+        <v>4.7425749999999995</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>293</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>44.014133333333341</v>
+        <v>4.4635999999999996</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>730</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
+++ b/Impressao 3D/CUSTO PEÇAS IMPRESSAS.xlsx
@@ -1717,19 +1717,19 @@
       </c>
       <c r="G4" s="19">
         <f t="shared" ref="G4:G9" si="0">$B$18*(1+F4/100)</f>
-        <v>11.158999999999999</v>
+        <v>16.991199999999999</v>
       </c>
       <c r="H4" s="19">
         <f t="shared" ref="H4:H9" si="1">G4*E4</f>
-        <v>11.158999999999999</v>
+        <v>16.991199999999999</v>
       </c>
       <c r="I4" s="19">
         <f t="shared" ref="I4:I9" si="2">G4-$B$18</f>
-        <v>8.3692499999999992</v>
+        <v>12.743399999999999</v>
       </c>
       <c r="J4" s="19">
         <f t="shared" ref="J4:J9" si="3">I4*E4</f>
-        <v>8.3692499999999992</v>
+        <v>12.743399999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1747,19 +1747,19 @@
       </c>
       <c r="G5" s="19">
         <f t="shared" si="0"/>
-        <v>9.7641249999999999</v>
+        <v>14.8673</v>
       </c>
       <c r="H5" s="19">
         <f t="shared" si="1"/>
-        <v>48.820625</v>
+        <v>74.336500000000001</v>
       </c>
       <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>6.9743750000000002</v>
+        <v>10.6195</v>
       </c>
       <c r="J5" s="19">
         <f t="shared" si="3"/>
-        <v>34.871875000000003</v>
+        <v>53.097500000000004</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1767,7 +1767,7 @@
         <v>58</v>
       </c>
       <c r="B6" s="23">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E6" s="3">
         <v>10</v>
@@ -1777,19 +1777,19 @@
       </c>
       <c r="G6" s="19">
         <f t="shared" si="0"/>
-        <v>8.3692499999999992</v>
+        <v>12.743399999999999</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="1"/>
-        <v>83.692499999999995</v>
+        <v>127.434</v>
       </c>
       <c r="I6" s="19">
         <f t="shared" si="2"/>
-        <v>5.5794999999999995</v>
+        <v>8.4955999999999996</v>
       </c>
       <c r="J6" s="19">
         <f t="shared" si="3"/>
-        <v>55.794999999999995</v>
+        <v>84.955999999999989</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1797,7 +1797,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="23">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1807,19 +1807,19 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" si="0"/>
-        <v>6.9743749999999993</v>
+        <v>10.619499999999999</v>
       </c>
       <c r="H7" s="19">
         <f t="shared" si="1"/>
-        <v>174.35937499999997</v>
+        <v>265.48749999999995</v>
       </c>
       <c r="I7" s="19">
         <f t="shared" si="2"/>
-        <v>4.1846249999999996</v>
+        <v>6.3716999999999988</v>
       </c>
       <c r="J7" s="19">
         <f t="shared" si="3"/>
-        <v>104.61562499999999</v>
+        <v>159.29249999999996</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>6.1374500000000003</v>
+        <v>9.3451599999999999</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="1"/>
-        <v>306.8725</v>
+        <v>467.25799999999998</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="2"/>
-        <v>3.3477000000000006</v>
+        <v>5.0973600000000001</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="3"/>
-        <v>167.38500000000002</v>
+        <v>254.86799999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>5.5794999999999995</v>
+        <v>8.4955999999999996</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="1"/>
-        <v>557.94999999999993</v>
+        <v>849.56</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="2"/>
-        <v>2.7897499999999997</v>
+        <v>4.2477999999999998</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" si="3"/>
-        <v>278.97499999999997</v>
+        <v>424.78</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1897,19 +1897,19 @@
       </c>
       <c r="G10" s="19">
         <f>$B$18*(1+F10/100)</f>
-        <v>5.0215499999999995</v>
+        <v>7.6460400000000002</v>
       </c>
       <c r="H10" s="19">
         <f>G10*E10</f>
-        <v>2510.7749999999996</v>
+        <v>3823.02</v>
       </c>
       <c r="I10" s="19">
         <f>G10-$B$18</f>
-        <v>2.2317999999999998</v>
+        <v>3.3982400000000004</v>
       </c>
       <c r="J10" s="19">
         <f>I10*E10</f>
-        <v>1115.8999999999999</v>
+        <v>1699.1200000000001</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="G11" s="19">
         <f>$B$18*(1+F11/100)</f>
-        <v>4.7425749999999995</v>
+        <v>7.2212599999999991</v>
       </c>
       <c r="H11" s="19">
         <f>G11*E11</f>
-        <v>4742.5749999999998</v>
+        <v>7221.2599999999993</v>
       </c>
       <c r="I11" s="19">
         <f>G11-$B$18</f>
-        <v>1.9528249999999998</v>
+        <v>2.9734599999999993</v>
       </c>
       <c r="J11" s="19">
         <f>I11*E11</f>
-        <v>1952.8249999999998</v>
+        <v>2973.4599999999991</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1951,19 +1951,19 @@
       </c>
       <c r="G12" s="19">
         <f>$B$18*(1+F12/100)</f>
-        <v>4.4635999999999996</v>
+        <v>6.7964799999999999</v>
       </c>
       <c r="H12" s="19">
         <f>G12*E12</f>
-        <v>11158.999999999998</v>
+        <v>16991.2</v>
       </c>
       <c r="I12" s="19">
         <f>G12-$B$18</f>
-        <v>1.6738499999999998</v>
+        <v>2.5486800000000001</v>
       </c>
       <c r="J12" s="19">
         <f>I12*E12</f>
-        <v>4184.625</v>
+        <v>6371.7</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B13" s="38">
         <f>B6/1000*VLOOKUP(B5,Configurações!$A$7:$B$11,2,FALSE)</f>
-        <v>1.08</v>
+        <v>2.88</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B14" s="38">
         <f>B7*0.25*Configurações!$B$4</f>
-        <v>0.44999999999999996</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B15" s="38">
         <f>VLOOKUP(B8,Configurações!$A$14:$B$22,2,FALSE)/(Configurações!$B$26*Configurações!$B$27)*B7</f>
-        <v>1.2597499999999999</v>
+        <v>1.0078</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B16" s="38">
         <f>B13+B14+B15</f>
-        <v>2.7897499999999997</v>
+        <v>4.2477999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B17" s="38">
         <f>IF(B9="SIM",B16*(1+Configurações!$B$33/100),B16)</f>
-        <v>2.7897499999999997</v>
+        <v>4.2477999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17</f>
-        <v>2.7897499999999997</v>
+        <v>4.2477999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J20" s="13">
         <f>B18*Configurações!$B$30/100</f>
-        <v>0.55794999999999995</v>
+        <v>0.84955999999999987</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="C13" s="27">
         <f>Calculadora!G4</f>
-        <v>11.158999999999999</v>
+        <v>16.991199999999999</v>
       </c>
       <c r="D13" s="39">
         <f>ROUNDUP((Calculadora!B7+12)/24,0)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C14" s="26">
         <f>Calculadora!G5</f>
-        <v>9.7641249999999999</v>
+        <v>14.8673</v>
       </c>
       <c r="D14" s="40">
         <f>ROUNDUP(((Calculadora!B7*B14+12)/Calculadora!B10)/24,0)</f>
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C15" s="27">
         <f>Calculadora!G6</f>
-        <v>8.3692499999999992</v>
+        <v>12.743399999999999</v>
       </c>
       <c r="D15" s="39">
         <f>ROUNDUP((Calculadora!B7*B15+12)/Calculadora!B10/24,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:4">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C16" s="26">
         <f>Calculadora!G7</f>
-        <v>6.9743749999999993</v>
+        <v>10.619499999999999</v>
       </c>
       <c r="D16" s="40">
         <f>ROUNDUP((Calculadora!B7*B16+12)/Calculadora!B10/24,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:4">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C17" s="27">
         <f>Calculadora!G8</f>
-        <v>6.1374500000000003</v>
+        <v>9.3451599999999999</v>
       </c>
       <c r="D17" s="39">
         <f>ROUNDUP((Calculadora!B7*B17+12)/Calculadora!B10/24,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2197,11 +2197,11 @@
       </c>
       <c r="C18" s="26">
         <f>Calculadora!G9</f>
-        <v>5.5794999999999995</v>
+        <v>8.4955999999999996</v>
       </c>
       <c r="D18" s="40">
         <f>ROUNDUP((Calculadora!B7*B18+12)/Calculadora!B10/24,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="C19" s="27">
         <f>Calculadora!G10</f>
-        <v>5.0215499999999995</v>
+        <v>7.6460400000000002</v>
       </c>
       <c r="D19" s="39">
         <f>ROUNDUP((Calculadora!B7*B19+12)/Calculadora!B10/24,0)</f>
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -2225,11 +2225,11 @@
       </c>
       <c r="C20" s="26">
         <f>Calculadora!G11</f>
-        <v>4.7425749999999995</v>
+        <v>7.2212599999999991</v>
       </c>
       <c r="D20" s="40">
         <f>ROUNDUP((Calculadora!B7*B20+12)/Calculadora!B10/24,0)</f>
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C21" s="27">
         <f>Calculadora!G12</f>
-        <v>4.4635999999999996</v>
+        <v>6.7964799999999999</v>
       </c>
       <c r="D21" s="39">
         <f>ROUNDUP((Calculadora!B7*B21+12)/Calculadora!B10/24,0)</f>
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
